--- a/data/dividends_info_20260626.xlsx
+++ b/data/dividends_info_20260626.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63.08000183105469</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1426759628844723</v>
+        <v>0.1438159114200256</v>
       </c>
       <c r="J2" t="n">
         <v>262</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.5</v>
+        <v>64.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.085271317829457</v>
+        <v>1.081081081081081</v>
       </c>
       <c r="J3" t="n">
         <v>241</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6396588408098992</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>171</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>63.08000183105469</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1426759628844723</v>
+        <v>0.1438159114200256</v>
       </c>
       <c r="J6" t="n">
         <v>171</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.029999971389771</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.79310350173476</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>150</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.29000091552734</v>
+        <v>20.21500015258789</v>
       </c>
       <c r="I8" t="n">
-        <v>1.330704720635951</v>
+        <v>1.335641840029544</v>
       </c>
       <c r="J8" t="n">
         <v>150</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.920000076293945</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I9" t="n">
-        <v>3.378378334839559</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J9" t="n">
         <v>143</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.550000190734863</v>
+        <v>7.650000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7947019666784939</v>
+        <v>0.7843137157126817</v>
       </c>
       <c r="J10" t="n">
         <v>115</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>94</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.29000091552734</v>
+        <v>20.21500015258789</v>
       </c>
       <c r="I14" t="n">
-        <v>1.330704720635951</v>
+        <v>1.335641840029544</v>
       </c>
       <c r="J14" t="n">
         <v>87</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>63.08000183105469</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1426759628844723</v>
+        <v>0.1438159114200256</v>
       </c>
       <c r="J15" t="n">
         <v>87</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.940000057220459</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I16" t="n">
-        <v>5.050505001853162</v>
+        <v>5.03355701476259</v>
       </c>
       <c r="J16" t="n">
         <v>80</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>38</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.489999771118164</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="I19" t="n">
-        <v>4.553734251779063</v>
+        <v>4.528985522895569</v>
       </c>
       <c r="J19" t="n">
         <v>31</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.990000009536743</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I20" t="n">
-        <v>3.508771921438032</v>
+        <v>3.414634225767048</v>
       </c>
       <c r="J20" t="n">
         <v>24</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.07800006866455</v>
+        <v>10.09799957275391</v>
       </c>
       <c r="I21" t="n">
-        <v>2.579876942136725</v>
+        <v>2.574767389587969</v>
       </c>
       <c r="J21" t="n">
         <v>24</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.76000022888184</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>4.065040587370328</v>
+        <v>4.05405400180747</v>
       </c>
       <c r="J22" t="n">
         <v>24</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.822000026702881</v>
+        <v>2.842000007629395</v>
       </c>
       <c r="I23" t="n">
-        <v>7.795889366345604</v>
+        <v>7.741027424680031</v>
       </c>
       <c r="J23" t="n">
         <v>24</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.445000171661377</v>
+        <v>6.539999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>3.723816813151975</v>
+        <v>3.669724792047231</v>
       </c>
       <c r="J25" t="n">
         <v>24</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.980000019073486</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>5.03355701476259</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>17</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.339999914169312</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I30" t="n">
-        <v>3.63247876571716</v>
+        <v>3.695652250531492</v>
       </c>
       <c r="J30" t="n">
         <v>10</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.45000076293945</v>
+        <v>34.70000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4354136333180191</v>
+        <v>0.4322766475561697</v>
       </c>
       <c r="J32" t="n">
         <v>10</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.86000061035156</v>
+        <v>21.65999984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>1.143641322139832</v>
+        <v>1.154201300836433</v>
       </c>
       <c r="J34" t="n">
         <v>-4</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.5</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6610169491525424</v>
+        <v>0.6565656396996691</v>
       </c>
       <c r="J35" t="n">
         <v>-4</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.175000190734863</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I37" t="n">
-        <v>5.603864527758002</v>
+        <v>5.566218769225643</v>
       </c>
       <c r="J37" t="n">
         <v>-4</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.684000015258789</v>
+        <v>3.667999982833862</v>
       </c>
       <c r="I38" t="n">
-        <v>4.343105302315275</v>
+        <v>4.362050183991154</v>
       </c>
       <c r="J38" t="n">
         <v>-4</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.471999883651733</v>
+        <v>2.467999935150146</v>
       </c>
       <c r="I39" t="n">
-        <v>5.606796380396862</v>
+        <v>5.615883453885421</v>
       </c>
       <c r="J39" t="n">
         <v>-4</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>45.00249862670898</v>
+        <v>46.25500106811523</v>
       </c>
       <c r="I40" t="n">
-        <v>1.399922269262834</v>
+        <v>1.362014885854743</v>
       </c>
       <c r="J40" t="n">
         <v>-4</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.195000171661377</v>
+        <v>6.175000190734863</v>
       </c>
       <c r="I41" t="n">
-        <v>2.259886943029007</v>
+        <v>2.267206407702785</v>
       </c>
       <c r="J41" t="n">
         <v>-4</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.21999931335449</v>
+        <v>28.45999908447266</v>
       </c>
       <c r="I43" t="n">
-        <v>3.012048266059866</v>
+        <v>2.986648022992197</v>
       </c>
       <c r="J43" t="n">
         <v>-4</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>63.08000183105469</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1426759628844723</v>
+        <v>0.1438159114200256</v>
       </c>
       <c r="J44" t="n">
         <v>-4</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.360000014305115</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7352941099128922</v>
+        <v>0.7246376836632911</v>
       </c>
       <c r="J45" t="n">
         <v>-4</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.315999984741211</v>
+        <v>6.288000106811523</v>
       </c>
       <c r="I46" t="n">
-        <v>2.870487657346448</v>
+        <v>2.883269671124932</v>
       </c>
       <c r="J46" t="n">
         <v>-4</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.640000343322754</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="I47" t="n">
-        <v>3.009259139682045</v>
+        <v>2.978236124092589</v>
       </c>
       <c r="J47" t="n">
         <v>-4</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.27000045776367</v>
+        <v>10.26500034332275</v>
       </c>
       <c r="I48" t="n">
-        <v>2.697176121259081</v>
+        <v>2.698489924359183</v>
       </c>
       <c r="J48" t="n">
         <v>-4</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9879999756813049</v>
+        <v>0.9860000014305115</v>
       </c>
       <c r="I49" t="n">
-        <v>1.366396794766181</v>
+        <v>1.369168355011551</v>
       </c>
       <c r="J49" t="n">
         <v>-11</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.946000099182129</v>
+        <v>2.95199990272522</v>
       </c>
       <c r="I50" t="n">
-        <v>3.733876316926747</v>
+        <v>3.726287385661852</v>
       </c>
       <c r="J50" t="n">
         <v>-11</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.950000047683716</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>1.230769200673001</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>-11</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.019999980926514</v>
+        <v>2.990000009536743</v>
       </c>
       <c r="I52" t="n">
-        <v>5.298013278493903</v>
+        <v>5.351170551494067</v>
       </c>
       <c r="J52" t="n">
         <v>-18</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8600000143051147</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="I53" t="n">
-        <v>2.90697669583182</v>
+        <v>2.94117638809046</v>
       </c>
       <c r="J53" t="n">
         <v>-18</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.64999961853027</v>
+        <v>27.75</v>
       </c>
       <c r="I54" t="n">
-        <v>4.014466601497197</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>-22</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8820000290870667</v>
+        <v>0.875</v>
       </c>
       <c r="I55" t="n">
-        <v>3.401360432045807</v>
+        <v>3.428571428571429</v>
       </c>
       <c r="J55" t="n">
         <v>-25</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4560000002384186</v>
       </c>
       <c r="I56" t="n">
-        <v>4.956896694357135</v>
+        <v>5.043859646485636</v>
       </c>
       <c r="J56" t="n">
         <v>-25</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8.840000152587891</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I58" t="n">
-        <v>2.262443399861825</v>
+        <v>2.272727223467237</v>
       </c>
       <c r="J58" t="n">
         <v>-25</v>
@@ -4650,44 +4650,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>